--- a/output/pdf_financials_xlsx/RECO.xlsx
+++ b/output/pdf_financials_xlsx/RECO.xlsx
@@ -1254,16 +1254,16 @@
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>263.624008</v>
+        <v>-263.624008</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>70.42159100000001</v>
+        <v>-70.42159100000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>9.570144000000001</v>
+        <v>-9.570144000000001</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>24.602752</v>
+        <v>-24.602752</v>
       </c>
     </row>
     <row r="17">
@@ -1526,16 +1526,16 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>263.624008</v>
+        <v>-263.624008</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>70.42159100000001</v>
+        <v>-70.42159100000001</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>9.570144000000001</v>
+        <v>-9.570144000000001</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>24.602752</v>
+        <v>-24.602752</v>
       </c>
     </row>
     <row r="21">
@@ -1686,16 +1686,16 @@
         <v>-7.479675</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>263.624008</v>
+        <v>-263.624008</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>70.42159100000001</v>
+        <v>-70.42159100000001</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>9.570144000000001</v>
+        <v>-9.570144000000001</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>24.602752</v>
+        <v>-24.602752</v>
       </c>
     </row>
     <row r="24">
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>164.765005</v>
+        <v>-164.765005</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>190.328624</v>
+        <v>-190.328624</v>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>263.624008</v>
+        <v>-263.624008</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>70.42159100000001</v>
+        <v>-70.42159100000001</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>9.570144000000001</v>
+        <v>-9.570144000000001</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>24.602752</v>
+        <v>-24.602752</v>
       </c>
     </row>
     <row r="28">
@@ -2028,16 +2028,16 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>263.658391</v>
+        <v>-263.589625</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>70.46014700000001</v>
+        <v>-70.38303500000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>9.570144000000001</v>
+        <v>-9.570144000000001</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>24.602752</v>
+        <v>-24.602752</v>
       </c>
     </row>
     <row r="30">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>2532.811336873553</v>
+        <v>-2532.150742292319</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>215.888949235808</v>
+        <v>-215.6526790978324</v>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
@@ -2160,16 +2160,16 @@
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>2532.481039582935</v>
+        <v>-2532.481039582935</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>215.7708141668202</v>
+        <v>-215.7708141668202</v>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
@@ -5378,43 +5378,43 @@
         <v>1.378246</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.378246</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.378246</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.378246</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.378246</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.378246</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.378246</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.378246</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.926603</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>10.951307</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>48.588119</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>73.080671</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>97.027192</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>109.322047</v>
       </c>
     </row>
     <row r="93">
@@ -5727,13 +5727,13 @@
         <v>-263.406976</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>70.42159100000001</v>
+        <v>-70.42159100000001</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>9.570144000000001</v>
+        <v>-9.570144000000001</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>24.602752</v>
+        <v>-24.602752</v>
       </c>
     </row>
     <row r="100">
@@ -9114,7 +9114,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11090,7 +11094,11 @@
           <t>Reserves (Note 10) 97,027,192</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -16538,7 +16546,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -25186,7 +25198,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -27886,7 +27902,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E225" s="5" t="n">
         <v>1.378246</v>
       </c>
@@ -28661,7 +28681,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -39309,19 +39333,19 @@
         <v>-1.873552</v>
       </c>
       <c r="F353" s="5" t="n">
-        <v>0.316021</v>
+        <v>-0.316021</v>
       </c>
       <c r="G353" s="5" t="n">
         <v>-1.266037</v>
       </c>
       <c r="H353" s="5" t="n">
-        <v>0.097307</v>
+        <v>-0.097307</v>
       </c>
       <c r="I353" s="5" t="n">
         <v>-0.270298</v>
       </c>
       <c r="J353" s="5" t="n">
-        <v>0.049043</v>
+        <v>-0.049043</v>
       </c>
       <c r="K353" t="inlineStr">
         <is>
@@ -42613,10 +42637,10 @@
         </is>
       </c>
       <c r="R389" s="5" t="n">
-        <v>9.570144000000001</v>
+        <v>-9.570144000000001</v>
       </c>
       <c r="S389" s="5" t="n">
-        <v>24.602752</v>
+        <v>-24.602752</v>
       </c>
     </row>
     <row r="390">
@@ -46211,10 +46235,10 @@
         </is>
       </c>
       <c r="P429" s="5" t="n">
-        <v>263.624008</v>
+        <v>-263.624008</v>
       </c>
       <c r="Q429" s="5" t="n">
-        <v>70.42159100000001</v>
+        <v>-70.42159100000001</v>
       </c>
       <c r="R429" t="inlineStr">
         <is>
@@ -52526,7 +52550,7 @@
         <v>-0.270298</v>
       </c>
       <c r="J500" s="5" t="n">
-        <v>0.049043</v>
+        <v>-0.049043</v>
       </c>
       <c r="K500" t="inlineStr">
         <is>
@@ -54496,7 +54520,7 @@
         <v>-1.266037</v>
       </c>
       <c r="H522" s="5" t="n">
-        <v>0.097307</v>
+        <v>-0.097307</v>
       </c>
       <c r="I522" t="inlineStr">
         <is>
@@ -56116,7 +56140,7 @@
         <v>-1.873552</v>
       </c>
       <c r="F540" s="5" t="n">
-        <v>0.316021</v>
+        <v>-0.316021</v>
       </c>
       <c r="G540" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RECO.xlsx
+++ b/output/pdf_financials_xlsx/RECO.xlsx
@@ -1003,22 +1003,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002045</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004586</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00125</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000794</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000426</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.873552</v>
+        <v>-1.875597</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.316021</v>
+        <v>-0.320607</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.266037</v>
+        <v>-1.267287</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.097307</v>
+        <v>-0.09810099999999999</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.270298</v>
+        <v>-0.270724</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.049043</v>
+        <v>-0.049118</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.125245</v>
@@ -1993,22 +1993,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.873552</v>
+        <v>-1.875597</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.28757</v>
+        <v>-0.292156</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.237586</v>
+        <v>-1.238836</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.097307</v>
+        <v>-0.09810099999999999</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.270298</v>
+        <v>-0.270724</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.049043</v>
+        <v>-0.049118</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.125245</v>
@@ -2264,49 +2264,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.9624549999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.570096</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.401222</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.236611</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.100688</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.18894</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.102436</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.158687</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.203642</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.547025</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>6.793395</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>61.153991</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>38.814806</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>11.413181</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>3.293122</v>
       </c>
     </row>
     <row r="35">
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.9624549999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.570096</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.401222</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.236611</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.100688</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.18894</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.102436</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.158687</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.203642</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.547025</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>6.793395</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>61.153991</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>38.814806</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>11.413181</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>3.293122</v>
       </c>
     </row>
     <row r="37">
@@ -2992,49 +2992,49 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.9757439999999999</v>
+        <v>0.013289</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.577306</v>
+        <v>0.00721</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.408391</v>
+        <v>0.007169</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.243343</v>
+        <v>0.006732</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.103113</v>
+        <v>0.002425</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.209663</v>
+        <v>0.020723</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.105257</v>
+        <v>0.002821</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.161689</v>
+        <v>0.003002</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.206346</v>
+        <v>0.002704</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.656974</v>
+        <v>0.109949</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>6.888898</v>
+        <v>0.095503</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>62.021473</v>
+        <v>0.867482</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>56.812141</v>
+        <v>17.997335</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>15.372206</v>
+        <v>3.959025</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>5.346386</v>
+        <v>2.053264</v>
       </c>
     </row>
     <row r="49">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -30038,7 +30038,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E249" s="5" t="n">
@@ -51447,7 +51447,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -53338,7 +53338,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -55862,7 +55862,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E537" s="5" t="n">
